--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487086_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487086_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4898</v>
+        <v>4.1685</v>
       </c>
       <c r="E2" t="n">
         <v>2.2068</v>
       </c>
       <c r="F2" t="n">
-        <v>2.283</v>
+        <v>1.9617</v>
       </c>
       <c r="G2" t="n">
         <v>1.4213</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2036</v>
+        <v>-0.1177</v>
       </c>
       <c r="T2" t="n">
         <v>0.1322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0713</v>
+        <v>-0.2499</v>
       </c>
       <c r="V2" t="n">
         <v>1.5138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2242</v>
+        <v>0.2963</v>
       </c>
       <c r="E3" t="n">
-        <v>4.53</v>
+        <v>5.1308</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.7542</v>
+        <v>-4.8345</v>
       </c>
       <c r="G3" t="n">
         <v>0.8289</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.316</v>
+        <v>-0.7955</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0562</v>
+        <v>-0.4554</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2598</v>
+        <v>-0.3401</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4926</v>
+        <v>0.2084</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.548</v>
+        <v>-0.8471</v>
       </c>
       <c r="F4" t="n">
         <v>1.0554</v>
@@ -766,10 +766,10 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7271</v>
+        <v>-0.0261</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8183</v>
+        <v>-0.1173</v>
       </c>
       <c r="U4" t="n">
         <v>0.0912</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0848</v>
+        <v>-0.8845</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0983</v>
+        <v>0.102</v>
       </c>
       <c r="F5" t="n">
         <v>-0.9865</v>
@@ -844,10 +844,10 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1481</v>
+        <v>0.0522</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1057</v>
+        <v>0.0945</v>
       </c>
       <c r="U5" t="n">
         <v>-0.0423</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2895</v>
+        <v>-1.1855</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0723</v>
+        <v>1.9747</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3618</v>
+        <v>-3.1602</v>
       </c>
       <c r="G6" t="n">
-        <v>2.778</v>
+        <v>0.4807</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0276</v>
+        <v>-0.1883</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7504</v>
+        <v>0.669</v>
       </c>
       <c r="J6" t="n">
-        <v>4.539</v>
+        <v>2.6364</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0078</v>
+        <v>1.4075</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5312</v>
+        <v>1.2288</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.761</v>
+        <v>-2.1557</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0198</v>
+        <v>-1.5959</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7808</v>
+        <v>-0.5598</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.8951</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0881</v>
+        <v>-0.386</v>
       </c>
       <c r="R6" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0555</v>
+        <v>-0.6312</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6214</v>
+        <v>-0.2756</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5658</v>
+        <v>-0.3556</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4929</v>
+        <v>-1.7833</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7745</v>
+        <v>1.4714</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2673</v>
+        <v>-3.2547</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4807</v>
+        <v>2.778</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1883</v>
+        <v>2.0276</v>
       </c>
       <c r="I7" t="n">
-        <v>0.669</v>
+        <v>0.7504</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6364</v>
+        <v>4.539</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4075</v>
+        <v>2.0078</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2288</v>
+        <v>2.5312</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1557</v>
+        <v>-1.761</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5959</v>
+        <v>0.0198</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5598</v>
+        <v>-1.7808</v>
       </c>
       <c r="P7" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-3.0881</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.193</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.386</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.579</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.9386</v>
+        <v>-0.4382</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4759</v>
+        <v>0.0205</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4627</v>
+        <v>-0.4587</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.34</v>
+        <v>-2.4643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2817</v>
+        <v>0.7901</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6217</v>
+        <v>-3.2544</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7881</v>
+        <v>-3.5024</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.3018</v>
+        <v>-3.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4863</v>
+        <v>-0.3891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6294</v>
+        <v>0.7752</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9578</v>
+        <v>-0.5022</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5873</v>
+        <v>1.2774</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.4176</v>
+        <v>-4.2776</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.344</v>
+        <v>-2.6111</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0735</v>
+        <v>-1.6665</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>2.3161</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1231</v>
+        <v>-0.193</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7021</v>
+        <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2551</v>
+        <v>-0.9921</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5897</v>
+        <v>0.2079</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3345</v>
+        <v>-1.2001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.614</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5717</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3652</v>
+        <v>-3.2154</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2908</v>
+        <v>-0.219</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.656</v>
+        <v>-2.9965</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5024</v>
+        <v>-3.7881</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1133</v>
+        <v>-3.3018</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3891</v>
+        <v>-0.4863</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7752</v>
+        <v>0.6294</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5022</v>
+        <v>-0.9578</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2774</v>
+        <v>1.5873</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.2776</v>
+        <v>-4.4176</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6111</v>
+        <v>-2.344</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6665</v>
+        <v>-2.0735</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5091</v>
+        <v>2.7021</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.893</v>
+        <v>-0.6203</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7086</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.6016</v>
+        <v>-0.7093</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0177</v>
+        <v>-4.8948</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4375</v>
+        <v>-3.8859</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5802</v>
+        <v>-1.009</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9798</v>
+        <v>-3.521</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9737</v>
+        <v>-2.3536</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0061</v>
+        <v>-1.1674</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.757</v>
+        <v>-2.5262</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1708</v>
+        <v>-1.2317</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2227</v>
+        <v>-0.9948</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8029</v>
+        <v>-1.1219</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4199</v>
+        <v>0.1271</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2888</v>
+        <v>-0.6018</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1917</v>
+        <v>-0.2016</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4805</v>
+        <v>-0.4002</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5561</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1754</v>
+        <v>-5.2378</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0861</v>
+        <v>-1.7379</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0893</v>
+        <v>-3.4999</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.521</v>
+        <v>-2.9798</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3536</v>
+        <v>-1.9737</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1674</v>
+        <v>-1.0061</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5262</v>
+        <v>-0.757</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2317</v>
+        <v>-0.1708</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2945</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9948</v>
+        <v>-2.2227</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1219</v>
+        <v>-1.8029</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1271</v>
+        <v>-0.4199</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.158</v>
       </c>
       <c r="R11" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8824</v>
+        <v>-0.509</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4019</v>
+        <v>-0.1087</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4805</v>
+        <v>-0.4002</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5561</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.9925</v>
+        <v>-14.9924</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9862</v>
+        <v>4.985900000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-19.9786</v>
@@ -1357,7 +1357,7 @@
         <v>-8.1427</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.075500000000002</v>
+        <v>-6.075500000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-2.0672</v>
@@ -1381,7 +1381,7 @@
         <v>-7.6972</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001000000000006551</v>
+        <v>0.0001000000000005996</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5104</v>
@@ -1390,10 +1390,10 @@
         <v>13.5105</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6798</v>
+        <v>-4.6797</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6144000000000001</v>
+        <v>-0.6146</v>
       </c>
       <c r="U12" t="n">
         <v>-4.0652</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.7247</v>
+        <v>9.2348</v>
       </c>
       <c r="E13" t="n">
-        <v>9.283799999999999</v>
+        <v>8.9154</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4409</v>
+        <v>0.3194</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9174</v>
+        <v>7.7185</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4883</v>
+        <v>2.9031</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4291</v>
+        <v>4.8154</v>
       </c>
       <c r="J13" t="n">
-        <v>6.1396</v>
+        <v>8.9862</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7373</v>
+        <v>4.0052</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4023</v>
+        <v>4.981</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2222</v>
+        <v>-1.2677</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.249</v>
+        <v>-1.1021</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9732</v>
+        <v>-0.1657</v>
       </c>
       <c r="P13" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7723</v>
+        <v>0.6392</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2323</v>
+        <v>0.2803</v>
       </c>
       <c r="U13" t="n">
-        <v>1.54</v>
+        <v>0.3589</v>
       </c>
       <c r="V13" t="n">
-        <v>1.842</v>
+        <v>0.4912</v>
       </c>
       <c r="W13" t="n">
-        <v>1.842</v>
+        <v>0.614</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.273099999999999</v>
+        <v>8.4063</v>
       </c>
       <c r="E14" t="n">
-        <v>8.1143</v>
+        <v>7.5814</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1588</v>
+        <v>0.8249</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7185</v>
+        <v>3.9174</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9031</v>
+        <v>1.4883</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8154</v>
+        <v>2.4291</v>
       </c>
       <c r="J14" t="n">
-        <v>8.9862</v>
+        <v>6.1396</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0052</v>
+        <v>2.7373</v>
       </c>
       <c r="L14" t="n">
-        <v>4.981</v>
+        <v>3.4023</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2677</v>
+        <v>-2.2222</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1021</v>
+        <v>-1.249</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1657</v>
+        <v>-0.9732</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3226</v>
+        <v>2.4539</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5208</v>
+        <v>1.5299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1983</v>
+        <v>0.924</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4912</v>
+        <v>1.842</v>
       </c>
       <c r="W14" t="n">
-        <v>0.614</v>
+        <v>1.842</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3632</v>
+        <v>4.342</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0786</v>
+        <v>3.9771</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2846</v>
+        <v>0.3649</v>
       </c>
       <c r="G15" t="n">
         <v>3.3398</v>
@@ -1624,13 +1624,13 @@
         <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3392</v>
+        <v>1.318</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9579</v>
+        <v>0.8563</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3814</v>
+        <v>0.4617</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1228</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2373</v>
+        <v>2.2005</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1659</v>
+        <v>1.8376</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9285</v>
+        <v>0.3628</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2377</v>
+        <v>-0.5456</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1002</v>
+        <v>0.2277</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8625</v>
+        <v>-0.7733</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3515</v>
+        <v>1.2422</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7749</v>
+        <v>1.1694</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4234</v>
+        <v>0.0728</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1138</v>
+        <v>-1.7878</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6747</v>
+        <v>-0.9417</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4391</v>
+        <v>-0.8461</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9571</v>
+        <v>0.7833</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8144</v>
+        <v>0.4399</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1427</v>
+        <v>0.3434</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3085</v>
+        <v>1.9628</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3085</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8177</v>
+        <v>1.0565</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9364</v>
+        <v>2.0657</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1187</v>
+        <v>-1.0092</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5456</v>
+        <v>0.2377</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2277</v>
+        <v>1.1002</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7733</v>
+        <v>-0.8625</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2422</v>
+        <v>1.3515</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1694</v>
+        <v>1.7749</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0728</v>
+        <v>-0.4234</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7878</v>
+        <v>-1.1138</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9417</v>
+        <v>-0.6747</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8461</v>
+        <v>-0.4391</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5995</v>
+        <v>0.7763</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4614</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1382</v>
+        <v>0.0621</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9628</v>
+        <v>-1.3085</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>-1.3085</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0533</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2541</v>
+        <v>0.1465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3073</v>
+        <v>0.6282</v>
       </c>
       <c r="G18" t="n">
         <v>0.9674</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9142</v>
+        <v>-0.1927</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5354</v>
+        <v>-0.1348</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3788</v>
+        <v>-0.0579</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.129</v>
+        <v>-1.1412</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6489</v>
+        <v>-0.1749</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4801</v>
+        <v>-0.9663</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0447</v>
+        <v>0.2294</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7594</v>
+        <v>0.6956</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7147</v>
+        <v>-0.4662</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03</v>
+        <v>1.7776</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5641</v>
+        <v>1.8111</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5941</v>
+        <v>-0.0335</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0747</v>
+        <v>-1.5482</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1953</v>
+        <v>-1.1155</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1207</v>
+        <v>-0.4327</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-4.8252</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9915</v>
+        <v>0.2264</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7139</v>
+        <v>0.4168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2776</v>
+        <v>-0.1904</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2859</v>
+        <v>1.1052</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>-1.3508</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.404</v>
+        <v>-2.0358</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8759</v>
+        <v>-1.4486</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5281</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2294</v>
+        <v>-1.0447</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6956</v>
+        <v>-1.7594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4662</v>
+        <v>0.7147</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7776</v>
+        <v>0.03</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8111</v>
+        <v>-0.5641</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0335</v>
+        <v>0.5941</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5482</v>
+        <v>-1.0747</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1155</v>
+        <v>-1.1953</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4327</v>
+        <v>0.1207</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7021</v>
+        <v>0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8252</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0364</v>
+        <v>-0.8983</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2842</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7522</v>
+        <v>-0.3847</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1052</v>
+        <v>-0.2859</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3508</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7001</v>
+        <v>-2.6803</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3454</v>
+        <v>-1.2452</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3547</v>
+        <v>-1.4351</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5866</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3774</v>
+        <v>0.3973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2062</v>
+        <v>0.3064</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1712</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5701</v>
+        <v>-3.824</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4166</v>
+        <v>-1.6169</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1535</v>
+        <v>-2.2071</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4765</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1573</v>
+        <v>-0.0965</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4297</v>
+        <v>0.2294</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2723</v>
+        <v>-0.3259</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2859</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.9926</v>
+        <v>15.66000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>19.9786</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.986</v>
+        <v>-4.3187</v>
       </c>
       <c r="G24" t="n">
         <v>8.142799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>13.5106</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6796</v>
+        <v>5.347399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>4.065300000000001</v>
+        <v>4.0653</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6145</v>
+        <v>1.2821</v>
       </c>
       <c r="V24" t="n">
         <v>2.170100000000001</v>
@@ -2341,7 +2341,7 @@
         <v>7.5693</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.3993</v>
+        <v>-5.399299999999999</v>
       </c>
     </row>
   </sheetData>
